--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076761</v>
       </c>
       <c r="B3" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076721</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076776</v>
       </c>
       <c r="B5" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076795</v>
       </c>
       <c r="B6" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>79139</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>75135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076781</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>75075</v>
+        <v>79170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462840</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149621</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>127076734</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>79092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076761</v>
       </c>
       <c r="B3" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076721</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076776</v>
       </c>
       <c r="B5" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076795</v>
       </c>
       <c r="B6" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>79173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R9" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B10" t="n">
-        <v>75135</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R10" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076725</v>
+        <v>127076781</v>
       </c>
       <c r="B11" t="n">
-        <v>79170</v>
+        <v>75138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462973</v>
+        <v>462840</v>
       </c>
       <c r="R11" t="n">
-        <v>7149469</v>
+        <v>7149621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>127076734</v>
       </c>
       <c r="B13" t="n">
-        <v>79092</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>79173</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>75138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076781</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>75138</v>
+        <v>79173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462840</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149621</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>75138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R9" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,32 +1516,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076781</v>
+        <v>127076725</v>
       </c>
       <c r="B10" t="n">
-        <v>75138</v>
+        <v>79173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462840</v>
+        <v>462973</v>
       </c>
       <c r="R10" t="n">
-        <v>7149621</v>
+        <v>7149469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B11" t="n">
-        <v>79173</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R11" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>75138</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,32 +1516,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076725</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>79173</v>
+        <v>75138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462973</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149469</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>79173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076721</v>
+        <v>127076776</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462973</v>
+        <v>462868</v>
       </c>
       <c r="R4" t="n">
-        <v>7149469</v>
+        <v>7149557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076776</v>
+        <v>127076721</v>
       </c>
       <c r="B5" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462868</v>
+        <v>462973</v>
       </c>
       <c r="R5" t="n">
-        <v>7149557</v>
+        <v>7149469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>79173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R9" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B10" t="n">
-        <v>75138</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R10" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076725</v>
+        <v>127076781</v>
       </c>
       <c r="B11" t="n">
-        <v>79173</v>
+        <v>75138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462973</v>
+        <v>462840</v>
       </c>
       <c r="R11" t="n">
-        <v>7149469</v>
+        <v>7149621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076761</v>
       </c>
       <c r="B3" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076776</v>
       </c>
       <c r="B4" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076721</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076795</v>
       </c>
       <c r="B6" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>79173</v>
+        <v>79177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>75142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B11" t="n">
-        <v>75138</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R11" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>127076734</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>79177</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>79177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>79177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R9" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B10" t="n">
-        <v>75142</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R10" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076725</v>
+        <v>127076781</v>
       </c>
       <c r="B11" t="n">
-        <v>79177</v>
+        <v>75142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462973</v>
+        <v>462840</v>
       </c>
       <c r="R11" t="n">
-        <v>7149469</v>
+        <v>7149621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076776</v>
+        <v>127076721</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462868</v>
+        <v>462973</v>
       </c>
       <c r="R4" t="n">
-        <v>7149557</v>
+        <v>7149469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076721</v>
+        <v>127076776</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462973</v>
+        <v>462868</v>
       </c>
       <c r="R5" t="n">
-        <v>7149469</v>
+        <v>7149557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076761</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076721</v>
+        <v>127076776</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>80124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462973</v>
+        <v>462868</v>
       </c>
       <c r="R4" t="n">
-        <v>7149469</v>
+        <v>7149557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076776</v>
+        <v>127076721</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462868</v>
+        <v>462973</v>
       </c>
       <c r="R5" t="n">
-        <v>7149557</v>
+        <v>7149469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
         <v>127076795</v>
       </c>
       <c r="B6" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>79177</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>127076759</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>127076781</v>
       </c>
       <c r="B11" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>127076734</v>
       </c>
       <c r="B13" t="n">
-        <v>79099</v>
+        <v>79101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>75144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076781</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462840</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149621</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076776</v>
+        <v>127076721</v>
       </c>
       <c r="B4" t="n">
-        <v>80124</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462868</v>
+        <v>462973</v>
       </c>
       <c r="R4" t="n">
-        <v>7149557</v>
+        <v>7149469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076721</v>
+        <v>127076776</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462973</v>
+        <v>462868</v>
       </c>
       <c r="R5" t="n">
-        <v>7149469</v>
+        <v>7149557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076759</v>
+        <v>127076725</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462925</v>
+        <v>462973</v>
       </c>
       <c r="R9" t="n">
-        <v>7149470</v>
+        <v>7149469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076781</v>
+        <v>127076759</v>
       </c>
       <c r="B10" t="n">
-        <v>75144</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462840</v>
+        <v>462925</v>
       </c>
       <c r="R10" t="n">
-        <v>7149621</v>
+        <v>7149470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076725</v>
+        <v>127076781</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>75144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462973</v>
+        <v>462840</v>
       </c>
       <c r="R11" t="n">
-        <v>7149469</v>
+        <v>7149621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19885-2025 artfynd.xlsx
+++ b/artfynd/A 19885-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127077041</v>
       </c>
       <c r="B2" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076761</v>
       </c>
       <c r="B3" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127076721</v>
+        <v>127076776</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>80127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462973</v>
+        <v>462868</v>
       </c>
       <c r="R4" t="n">
-        <v>7149469</v>
+        <v>7149557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127076776</v>
+        <v>127076721</v>
       </c>
       <c r="B5" t="n">
-        <v>80124</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462868</v>
+        <v>462973</v>
       </c>
       <c r="R5" t="n">
-        <v>7149557</v>
+        <v>7149469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
         <v>127076795</v>
       </c>
       <c r="B6" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076750</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076770</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,32 +1411,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127076725</v>
+        <v>127076759</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462973</v>
+        <v>462925</v>
       </c>
       <c r="R9" t="n">
-        <v>7149469</v>
+        <v>7149470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127076759</v>
+        <v>127076781</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>75147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462925</v>
+        <v>462840</v>
       </c>
       <c r="R10" t="n">
-        <v>7149470</v>
+        <v>7149621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127076781</v>
+        <v>127076725</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462840</v>
+        <v>462973</v>
       </c>
       <c r="R11" t="n">
-        <v>7149621</v>
+        <v>7149469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>127076882</v>
       </c>
       <c r="B12" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>127076734</v>
       </c>
       <c r="B13" t="n">
-        <v>79101</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127077013</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
